--- a/files/Commonwealth_Netball_upcoming_projections.xlsx
+++ b/files/Commonwealth_Netball_upcoming_projections.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Configuration" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projections'!$A$1:$AH$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projections'!$A$1:$AH$3</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t xml:space="preserve">model_version</t>
   </si>
@@ -123,94 +123,43 @@
     <t xml:space="preserve">commonwealth_netball_winston_scorereg_v2</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 14:04:37 AEST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
+    <t xml:space="preserve">2026-08-02 14:49:28 AEST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
   </si>
   <si>
     <t xml:space="preserve">single_score_head_geometric_wls_decay_0.92</t>
   </si>
   <si>
-    <t xml:space="preserve">30-Jul-2026 18:00</t>
+    <t xml:space="preserve">02-Aug-2026 18:00</t>
   </si>
   <si>
     <t xml:space="preserve">Commonwealth Games</t>
   </si>
   <si>
-    <t xml:space="preserve">Malawi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tonga</t>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">England</t>
   </si>
   <si>
     <t xml:space="preserve">identified</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 14:04:36 AEST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.flashscore.com.au/match/netball/malawi-EoA0csHu/tonga-tKG3iRli/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-Jul-2026 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uganda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scotland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.flashscore.com.au/match/netball/scotland-h6pL0pxs/uganda-S8zoKzzD/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30-Jul-2026 23:00</t>
+    <t xml:space="preserve">https://www.flashscore.com.au/match/netball/australia-KSx9gkKU/england-dOWvft6I/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02-Aug-2026 22:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamaica</t>
   </si>
   <si>
     <t xml:space="preserve">New Zealand</t>
   </si>
   <si>
-    <t xml:space="preserve">Trinidad &amp; Tobago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.flashscore.com.au/match/netball/new-zealand-txv5fV4O/trinidad-tobago-d8EnZlV9/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31-Jul-2026 01:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northern Ireland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.flashscore.com.au/match/netball/australia-KSx9gkKU/northern-ireland-QJrTbO6g/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31-Jul-2026 04:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamaica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.flashscore.com.au/match/netball/jamaica-vFQwEb86/wales-WdqPa4im/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31-Jul-2026 06:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">England</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Africa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.flashscore.com.au/match/netball/england-dOWvft6I/south-africa-8lVsDINC/</t>
+    <t xml:space="preserve">https://www.flashscore.com.au/match/netball/jamaica-vFQwEb86/new-zealand-txv5fV4O/</t>
   </si>
   <si>
     <t xml:space="preserve">data_through</t>
@@ -237,7 +186,10 @@
     <t xml:space="preserve">recency_decay</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 14:03:47 AEST</t>
+    <t xml:space="preserve">2026-08-02 14:48:00 AEST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-01</t>
   </si>
   <si>
     <t xml:space="preserve">2022-07-29</t>
@@ -603,8 +555,8 @@
     <col min="7" max="7" width="24.0336147064084" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="12.3718073532042" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="18.7099996496707" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="11.7099997859099" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="21.7099995912824" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="11.2056266178838" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="11.7099997859099" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="24.0336147064084" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="24.0336147064084" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="25.1997954417288" hidden="0" customWidth="1"/>
@@ -627,7 +579,7 @@
     <col min="31" max="31" width="21.7012532357675" hidden="0" customWidth="1"/>
     <col min="32" max="32" width="29.8645183830105" hidden="0" customWidth="1"/>
     <col min="33" max="33" width="24.7099995328942" hidden="0" customWidth="1"/>
-    <col min="34" max="34" width="90.7099982483533" hidden="0" customWidth="1"/>
+    <col min="34" max="34" width="82.7099984040552" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -757,7 +709,7 @@
         <v>38</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="I2" t="s">
         <v>39</v>
@@ -769,46 +721,46 @@
         <v>41</v>
       </c>
       <c r="L2" t="n">
-        <v>63.5</v>
+        <v>61.9</v>
       </c>
       <c r="M2" t="n">
-        <v>51.48</v>
+        <v>53.24</v>
       </c>
       <c r="N2" t="n">
-        <v>12.02</v>
+        <v>8.65</v>
       </c>
       <c r="O2" t="n">
-        <v>-12.02</v>
+        <v>-8.65</v>
       </c>
       <c r="P2" t="n">
-        <v>114.99</v>
+        <v>115.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>22.23</v>
+        <v>43.5</v>
       </c>
       <c r="R2" t="n">
-        <v>20.61</v>
+        <v>36.12</v>
       </c>
       <c r="S2" t="n">
-        <v>42.84</v>
+        <v>79.61</v>
       </c>
       <c r="T2" t="n">
-        <v>21.79</v>
+        <v>39.06</v>
       </c>
       <c r="U2" t="n">
-        <v>9.03</v>
+        <v>31.9</v>
       </c>
       <c r="V2" t="n">
-        <v>30.82</v>
+        <v>70.96</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="Y2" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
@@ -829,13 +781,13 @@
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.02</v>
+        <v>8.65</v>
       </c>
       <c r="AG2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH2" t="s">
         <v>43</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -858,61 +810,61 @@
         <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46233</v>
+        <v>46236</v>
       </c>
       <c r="I3" t="s">
         <v>39</v>
       </c>
       <c r="J3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" t="s">
         <v>46</v>
       </c>
-      <c r="K3" t="s">
-        <v>47</v>
-      </c>
       <c r="L3" t="n">
-        <v>58.49</v>
+        <v>47.77</v>
       </c>
       <c r="M3" t="n">
-        <v>42.2</v>
+        <v>57.87</v>
       </c>
       <c r="N3" t="n">
-        <v>16.29</v>
+        <v>-10.11</v>
       </c>
       <c r="O3" t="n">
-        <v>-16.29</v>
+        <v>10.11</v>
       </c>
       <c r="P3" t="n">
-        <v>100.69</v>
+        <v>105.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>27.37</v>
+        <v>30.04</v>
       </c>
       <c r="R3" t="n">
-        <v>24.45</v>
+        <v>30.9</v>
       </c>
       <c r="S3" t="n">
-        <v>51.83</v>
+        <v>60.94</v>
       </c>
       <c r="T3" t="n">
-        <v>16.35</v>
+        <v>38.46</v>
       </c>
       <c r="U3" t="n">
-        <v>19.19</v>
+        <v>32.58</v>
       </c>
       <c r="V3" t="n">
-        <v>35.54</v>
+        <v>71.04</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="Y3" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
@@ -933,433 +885,17 @@
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>16.29</v>
+        <v>-10.11</v>
       </c>
       <c r="AG3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="AH3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="I4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" t="s">
-        <v>50</v>
-      </c>
-      <c r="K4" t="s">
-        <v>51</v>
-      </c>
-      <c r="L4" t="n">
-        <v>87.08</v>
-      </c>
-      <c r="M4" t="n">
-        <v>20.87</v>
-      </c>
-      <c r="N4" t="n">
-        <v>66.21</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-66.21</v>
-      </c>
-      <c r="P4" t="n">
-        <v>107.95</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>40.19</v>
-      </c>
-      <c r="R4" t="n">
-        <v>33.56</v>
-      </c>
-      <c r="S4" t="n">
-        <v>73.75</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="V4" t="n">
-        <v>7.54</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>55</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>66.21</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="I5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K5" t="s">
-        <v>55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>83.6</v>
-      </c>
-      <c r="M5" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="N5" t="n">
-        <v>60.48</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-60.48</v>
-      </c>
-      <c r="P5" t="n">
-        <v>106.72</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="R5" t="n">
-        <v>36.48</v>
-      </c>
-      <c r="S5" t="n">
-        <v>82.28</v>
-      </c>
-      <c r="T5" t="n">
-        <v>9.29</v>
-      </c>
-      <c r="U5" t="n">
-        <v>12.51</v>
-      </c>
-      <c r="V5" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>54</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>60.48</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="I6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L6" t="n">
-        <v>69.03</v>
-      </c>
-      <c r="M6" t="n">
-        <v>42.55</v>
-      </c>
-      <c r="N6" t="n">
-        <v>26.48</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-26.48</v>
-      </c>
-      <c r="P6" t="n">
-        <v>111.57</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>31.15</v>
-      </c>
-      <c r="R6" t="n">
-        <v>28.85</v>
-      </c>
-      <c r="S6" t="n">
-        <v>59.99</v>
-      </c>
-      <c r="T6" t="n">
-        <v>21.08</v>
-      </c>
-      <c r="U6" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="V6" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>35</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>26.48</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>46234</v>
-      </c>
-      <c r="I7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" t="s">
-        <v>62</v>
-      </c>
-      <c r="K7" t="s">
-        <v>63</v>
-      </c>
-      <c r="L7" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-6.65</v>
-      </c>
-      <c r="P7" t="n">
-        <v>113.75</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>38.18</v>
-      </c>
-      <c r="R7" t="n">
-        <v>32.44</v>
-      </c>
-      <c r="S7" t="n">
-        <v>70.62</v>
-      </c>
-      <c r="T7" t="n">
-        <v>35.69</v>
-      </c>
-      <c r="U7" t="n">
-        <v>28.29</v>
-      </c>
-      <c r="V7" t="n">
-        <v>63.97</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>60</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>41</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AH7"/>
+  <autoFilter ref="A1:AH3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -1395,31 +931,31 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E1" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F1" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="H1" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="I1" t="s">
         <v>22</v>
       </c>
       <c r="J1" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="K1" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="L1" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2">
@@ -1430,22 +966,22 @@
         <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
